--- a/output/graficos_dimensiones/comunal_i_peringrmin_a_2021_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringrmin_a_2021_metropolitana.xlsx
@@ -132,12 +132,12 @@
     <t xml:space="preserve">Cerrillos</t>
   </si>
   <si>
+    <t xml:space="preserve">Peñaflor</t>
+  </si>
+  <si>
     <t xml:space="preserve">La Cisterna</t>
   </si>
   <si>
-    <t xml:space="preserve">Peñaflor</t>
-  </si>
-  <si>
     <t xml:space="preserve">Padre Hurtado</t>
   </si>
   <si>
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:34</t>
+    <t xml:space="preserve">2026-09-09 23:32</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -1175,7 +1175,7 @@
         <v>38</v>
       </c>
       <c r="C34" s="2" t="n">
-        <v>13109</v>
+        <v>13605</v>
       </c>
       <c r="D34" s="2" t="n">
         <v>2021</v>
@@ -1192,7 +1192,7 @@
         <v>39</v>
       </c>
       <c r="C35" s="2" t="n">
-        <v>13605</v>
+        <v>13109</v>
       </c>
       <c r="D35" s="2" t="n">
         <v>2021</v>

--- a/output/graficos_dimensiones/comunal_i_peringrmin_a_2021_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringrmin_a_2021_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:32</t>
+    <t xml:space="preserve">2026-09-17 14:26</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_peringrmin_a_2021_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringrmin_a_2021_metropolitana.xlsx
@@ -132,12 +132,12 @@
     <t xml:space="preserve">Cerrillos</t>
   </si>
   <si>
+    <t xml:space="preserve">La Cisterna</t>
+  </si>
+  <si>
     <t xml:space="preserve">Peñaflor</t>
   </si>
   <si>
-    <t xml:space="preserve">La Cisterna</t>
-  </si>
-  <si>
     <t xml:space="preserve">Padre Hurtado</t>
   </si>
   <si>
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 14:26</t>
+    <t xml:space="preserve">2026-09-23 12:54</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -1175,7 +1175,7 @@
         <v>38</v>
       </c>
       <c r="C34" s="2" t="n">
-        <v>13605</v>
+        <v>13109</v>
       </c>
       <c r="D34" s="2" t="n">
         <v>2021</v>
@@ -1192,7 +1192,7 @@
         <v>39</v>
       </c>
       <c r="C35" s="2" t="n">
-        <v>13109</v>
+        <v>13605</v>
       </c>
       <c r="D35" s="2" t="n">
         <v>2021</v>
@@ -1500,7 +1500,9 @@
       <c r="C53" s="2" t="n">
         <v>13303</v>
       </c>
-      <c r="D53" s="2"/>
+      <c r="D53" s="2" t="n">
+        <v>2021</v>
+      </c>
       <c r="E53" s="2"/>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_i_peringrmin_a_2021_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringrmin_a_2021_metropolitana.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="72">
   <si>
     <t xml:space="preserve">Región</t>
   </si>
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:54</t>
+    <t xml:space="preserve">2026-10-01 23:21</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -219,7 +219,7 @@
     <t xml:space="preserve">Indicador</t>
   </si>
   <si>
-    <t xml:space="preserve">Ingreso sobre salario mínimo (%)</t>
+    <t xml:space="preserve">% con ingreso igual al mínimo</t>
   </si>
   <si>
     <t xml:space="preserve">Unidad territorial</t>
@@ -232,9 +232,6 @@
   </si>
   <si>
     <t xml:space="preserve">Unidad de medida</t>
-  </si>
-  <si>
-    <t xml:space="preserve">% sobre salario mínimo</t>
   </si>
 </sst>
 </file>
@@ -1582,7 +1579,7 @@
         <v>71</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_i_peringrmin_a_2021_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringrmin_a_2021_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:21</t>
+    <t xml:space="preserve">2026-10-02 11:26</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_peringrmin_a_2021_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringrmin_a_2021_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 11:26</t>
+    <t xml:space="preserve">2026-10-02 15:22</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_peringrmin_a_2021_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringrmin_a_2021_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 15:22</t>
+    <t xml:space="preserve">2026-10-05 12:46</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
